--- a/healthcare_forms/023_sugar_intake_survey--healthcare_forms.xlsx
+++ b/healthcare_forms/023_sugar_intake_survey--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'less_than_10_grams'}</t>
+          <t>less_than_10_grams</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Less than 10 grams'}</t>
+          <t>Less than 10 grams</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'10_to_20_grams'}</t>
+          <t>10_to_20_grams</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': '10 to 20 grams'}</t>
+          <t>10 to 20 grams</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'20_to_30_grams'}</t>
+          <t>20_to_30_grams</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': '20 to 30 grams'}</t>
+          <t>20 to 30 grams</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'more_than_30_grams'}</t>
+          <t>more_than_30_grams</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'More than 30 grams'}</t>
+          <t>More than 30 grams</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'white_sugar'}</t>
+          <t>white_sugar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'White sugar'}</t>
+          <t>White sugar</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'brown_sugar'}</t>
+          <t>brown_sugar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Brown sugar'}</t>
+          <t>Brown sugar</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'honey'}</t>
+          <t>honey</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Honey'}</t>
+          <t>Honey</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'artificial_sweeteners'}</t>
+          <t>artificial_sweeteners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Artificial sweeteners'}</t>
+          <t>Artificial sweeteners</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'text':_'fruit'}</t>
+          <t>fruit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'text': 'Fruit'}</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
